--- a/data/trans_orig/IP31KM11_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM11_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>52409</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>48778</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>97,6%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>90,84%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>44580</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>41138</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>45905</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>97,11%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>89,62%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>58345</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>142</t>
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>110753</t>
+          <t>98295</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>108043</t>
+          <t>95218</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1290</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4921</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4767</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>10,38%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>4402</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1290</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>454527</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>446517</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>459981</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>97,45%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>95,73%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>98,62%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>618</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>447379</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>442480</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>449968</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>99,01%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>97,93%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>488410</t>
+          <t>419875</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>464793</t>
+          <t>414399</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>496708</t>
+          <t>422652</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>935789</t>
+          <t>874403</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>911839</t>
+          <t>865784</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>945161</t>
+          <t>880546</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11896</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6442</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>19906</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4,27%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4453</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1864</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9352</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8542</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40457</t>
+          <t>10267</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>21293</t>
+          <t>16687</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11921</t>
+          <t>10544</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45243</t>
+          <t>25306</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,74 +1406,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>161844</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>157368</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>164480</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>97,1%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>94,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>98,68%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>145057</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>141853</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>97,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>146124</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>143308</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>147140</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>99,31%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>176091</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>170617</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>178913</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>97,21%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>94,19%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>445</t>
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>321147</t>
+          <t>307967</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>316242</t>
+          <t>302734</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>324310</t>
+          <t>310850</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4842</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2206</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9318</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1129</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4333</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3832</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>5048</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2226</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>10522</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>11091</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>670086</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>662166</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>676812</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>96,41%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>98,54%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>903</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>644845</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>639401</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>648204</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>722845</t>
+          <t>610580</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>699061</t>
+          <t>605009</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>731853</t>
+          <t>614005</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1367690</t>
+          <t>1280666</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1347234</t>
+          <t>1271217</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1377659</t>
+          <t>1288279</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16738</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10012</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>24658</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>6872</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3513</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12316</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21888</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12880</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45672</t>
+          <t>12702</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>28760</t>
+          <t>23869</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18791</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49216</t>
+          <t>33318</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
